--- a/dist/成果/防治对象/测量表/360481106205107_铺头何家/沟道纵断面成果表_AFAE90012A000000ZACS012.xlsx
+++ b/dist/成果/防治对象/测量表/360481106205107_铺头何家/沟道纵断面成果表_AFAE90012A000000ZACS012.xlsx
@@ -822,7 +822,7 @@
         <v>53.47799999999999</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>53.88220617221246</v>
+        <v>53.94381650332091</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>115.485755</v>
@@ -850,7 +850,7 @@
         <v>53.44</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>53.84508809641405</v>
+        <v>53.74955641681733</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>115.486496</v>
@@ -878,7 +878,7 @@
         <v>53.385</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>53.56496367412519</v>
+        <v>53.53220071101624</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>115.487194</v>
@@ -906,7 +906,7 @@
         <v>53.378</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>53.44020824767476</v>
+        <v>53.50130948405992</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>115.487784</v>
@@ -934,7 +934,7 @@
         <v>53.338</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>53.42798935371147</v>
+        <v>53.42161524156707</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>115.488296</v>
@@ -962,7 +962,7 @@
         <v>53.37</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>53.4578316407922</v>
+        <v>53.79391918225618</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>115.488337</v>
@@ -990,7 +990,7 @@
         <v>53.262</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>53.34642157068154</v>
+        <v>53.6564081369877</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>115.488479</v>
@@ -1018,7 +1018,7 @@
         <v>53.288</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>53.62331004434587</v>
+        <v>53.33396459888339</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>115.488521</v>
@@ -1046,7 +1046,7 @@
         <v>53.142</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>53.53769936645029</v>
+        <v>53.20775978966737</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>115.488565</v>
@@ -1074,7 +1074,7 @@
         <v>53.117</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>53.19933970258297</v>
+        <v>53.53927023916053</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>115.488694</v>
@@ -1102,7 +1102,7 @@
         <v>53.099</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>53.53744612761584</v>
+        <v>53.50714147818369</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>115.48883</v>
@@ -1130,7 +1130,7 @@
         <v>53.077</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>53.28289929521102</v>
+        <v>53.30771723882294</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>115.488965</v>
@@ -1158,7 +1158,7 @@
         <v>53.323</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>53.40109948284771</v>
+        <v>53.65633978094885</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>115.488949</v>
@@ -1186,7 +1186,7 @@
         <v>52.998</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>53.29484212980306</v>
+        <v>53.16932601045088</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>115.489086</v>
@@ -1214,7 +1214,7 @@
         <v>52.985</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>53.39066730289098</v>
+        <v>53.45233190638193</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>115.489196</v>
@@ -1242,7 +1242,7 @@
         <v>52.957</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>53.28629720255804</v>
+        <v>53.28515299289268</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>115.489549</v>
@@ -1270,7 +1270,7 @@
         <v>52.91099999999999</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>53.13434185907455</v>
+        <v>53.35622676293402</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>115.48974</v>
@@ -1298,7 +1298,7 @@
         <v>52.892</v>
       </c>
       <c r="F29" s="22" t="n">
-        <v>53.33732074962901</v>
+        <v>53.33183462830798</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>115.489992</v>
@@ -1326,7 +1326,7 @@
         <v>52.878</v>
       </c>
       <c r="F30" s="22" t="n">
-        <v>53.17414921617542</v>
+        <v>52.92623222404981</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>115.490251</v>
@@ -1354,7 +1354,7 @@
         <v>52.86499999999999</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>52.89588361210229</v>
+        <v>53.0920584634424</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>115.49105</v>
@@ -1378,16 +1378,16 @@
     <mergeCell ref="D3:H3"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"85高程系,假定高程系"</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"水准仪／卷尺测量法,GNSS RTK测量法,全站仪法,三维激光扫描方法"</formula1>
     </dataValidation>
   </dataValidations>
